--- a/data/trans_camb/IP18A05-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP18A05-Edad-trans_camb.xlsx
@@ -677,27 +677,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 0,0</t>
+          <t>-3,49; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,86</t>
+          <t>-2,8; 0,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 11,88</t>
+          <t>-1,38; 11,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,46</t>
+          <t>-1,35; 0,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,49</t>
+          <t>-0,67; 1,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 6,89</t>
+          <t>-0,34; 7,34</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 2,29</t>
+          <t>-0,22; 2,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,86</t>
+          <t>0,37; 4,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 13,12</t>
+          <t>0,0; 13,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,03</t>
+          <t>-0,34; 2,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,92</t>
+          <t>-0,88; 1,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 13,07</t>
+          <t>-0,3; 10,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,19</t>
+          <t>0,16; 2,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,33</t>
+          <t>0,1; 2,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 9,74</t>
+          <t>0,68; 9,33</t>
         </is>
       </c>
     </row>
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,85; —</t>
+          <t>-24,34; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,65; —</t>
+          <t>-24,81; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38,85; —</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 3,52</t>
+          <t>-2,08; 3,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 1,91</t>
+          <t>-3,38; 1,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 8,81</t>
+          <t>-2,2; 10,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 2,02</t>
+          <t>-2,48; 2,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 0,84</t>
+          <t>-3,34; 0,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 16,96</t>
+          <t>-0,83; 15,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 2,23</t>
+          <t>-1,3; 2,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,01</t>
+          <t>-1,93; 1,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 10,0</t>
+          <t>-0,28; 8,9</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-76,46; 690,98</t>
+          <t>-72,11; 692,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-89,93; 363,11</t>
+          <t>-89,5; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 0,0</t>
+          <t>-2,83; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 1,03</t>
+          <t>-1,7; 1,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 9,55</t>
+          <t>-1,09; 9,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,72</t>
+          <t>-1,13; 1,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,73</t>
+          <t>0,48; 6,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 17,53</t>
+          <t>-0,42; 17,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,65</t>
+          <t>-1,22; 0,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 3,2</t>
+          <t>-0,02; 3,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 13,27</t>
+          <t>0,0; 13,67</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,3; —</t>
+          <t>-38,23; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-62,3; 2527,43</t>
+          <t>-40,4; 1582,4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,02</t>
+          <t>-0,64; 1,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,48</t>
+          <t>-0,3; 1,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,27; 6,35</t>
+          <t>0,21; 5,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,46</t>
+          <t>-0,23; 1,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 1,94</t>
+          <t>0,03; 1,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 9,37</t>
+          <t>1,1; 8,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,98</t>
+          <t>-0,21; 0,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,36</t>
+          <t>0,06; 1,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,87</t>
+          <t>1,29; 5,97</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-64,21; 378,1</t>
+          <t>-64,24; 345,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-45,36; 642,13</t>
+          <t>-48,2; 507,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 2083,33</t>
+          <t>-22,09; 1973,84</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-32,26; 697,45</t>
+          <t>-43,28; 626,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,92; 732,12</t>
+          <t>-20,18; 801,19</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,9; 3292,96</t>
+          <t>77,55; 2683,06</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-31,19; 297,86</t>
+          <t>-25,52; 256,65</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 386,27</t>
+          <t>-3,21; 337,73</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>141,78; 1424,17</t>
+          <t>138,86; 1518,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A05-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP18A05-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,0</t>
+          <t>-3,76; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 0,86</t>
+          <t>-2,82; 0,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 11,82</t>
+          <t>-1,4; 10,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,82</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,1</t>
+          <t>0,0; 9,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,46</t>
+          <t>-1,36; 0,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,53</t>
+          <t>-0,68; 1,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 7,34</t>
+          <t>-0,34; 8,35</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 2,49</t>
+          <t>-0,21; 2,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,36</t>
+          <t>0,42; 4,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,69</t>
+          <t>-0,26; 12,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,82</t>
+          <t>-0,28; 3,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,96</t>
+          <t>-0,89; 1,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 10,55</t>
+          <t>-0,59; 12,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 2,04</t>
+          <t>0,04; 2,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,3</t>
+          <t>-0,01; 2,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 9,33</t>
+          <t>0,7; 8,84</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-66,27; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,34; —</t>
+          <t>-25,87; 1322,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,81; —</t>
+          <t>-59,89; 1500,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,85; —</t>
+          <t>-100,0; 5880,91</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 3,57</t>
+          <t>-1,96; 3,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 1,77</t>
+          <t>-3,22; 1,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 10,35</t>
+          <t>-2,25; 9,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 2,03</t>
+          <t>-2,47; 2,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,85</t>
+          <t>-3,59; 0,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 15,24</t>
+          <t>-0,83; 13,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 2,32</t>
+          <t>-1,33; 2,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,1</t>
+          <t>-1,97; 1,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 8,9</t>
+          <t>-0,68; 8,72</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-72,11; 692,41</t>
+          <t>-75,57; 627,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-89,5; —</t>
+          <t>-90,24; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 0,0</t>
+          <t>-2,77; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,05</t>
+          <t>-1,67; 1,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 9,94</t>
+          <t>-1,1; 9,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,69</t>
+          <t>-1,3; 1,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,39</t>
+          <t>0,46; 6,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 17,26</t>
+          <t>-0,41; 20,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,71</t>
+          <t>-1,17; 0,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 3,25</t>
+          <t>-0,09; 3,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,67</t>
+          <t>0,11; 11,7</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,23; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,4; 1582,4</t>
+          <t>-42,21; 2613,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,02</t>
+          <t>-0,64; 1,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,43</t>
+          <t>-0,26; 1,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 5,72</t>
+          <t>0,31; 5,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,42</t>
+          <t>-0,28; 1,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,86</t>
+          <t>-0,1; 1,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 8,53</t>
+          <t>1,2; 8,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,97</t>
+          <t>-0,18; 0,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,37</t>
+          <t>0,07; 1,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,97</t>
+          <t>1,24; 5,61</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-64,24; 345,79</t>
+          <t>-70,37; 416,36</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,2; 507,61</t>
+          <t>-39,25; 664,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,09; 1973,84</t>
+          <t>-27,18; 1789,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,28; 626,39</t>
+          <t>-42,58; 602,17</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,18; 801,19</t>
+          <t>-28,23; 698,18</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,55; 2683,06</t>
+          <t>92,77; 2998,07</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 256,65</t>
+          <t>-26,17; 291,77</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 337,73</t>
+          <t>2,41; 499,06</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>138,86; 1518,28</t>
+          <t>145,15; 1477,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A05-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP18A05-Edad-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,46</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,09</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,94</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,27</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,46</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,09</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,15</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>1,82</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,0</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 0,86</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 10,64</t>
+          <t>0,0; 9,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>-4,46; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>-2,85; 0,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,91</t>
+          <t>-1,38; 11,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,46</t>
+          <t>-1,12; 0,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,5</t>
+          <t>-0,66; 1,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 8,35</t>
+          <t>-0,34; 6,23</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-38,73%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>265,14%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>240,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>588,16%</t>
+          <t>536,2%</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,37</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,31</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,68</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,64</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,83</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>3,86</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,55</t>
+          <t>3,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,25</t>
+          <t>-0,33; 3,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,12</t>
+          <t>-0,89; 1,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 12,46</t>
+          <t>-0,59; 13,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 3,04</t>
+          <t>-0,19; 2,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,86</t>
+          <t>0,29; 3,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 12,68</t>
+          <t>-0,26; 13,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,03</t>
+          <t>0,11; 2,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 2,3</t>
+          <t>0,05; 2,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 8,84</t>
+          <t>0,68; 9,76</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>191,54%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>62,91%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>557,91%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>263,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>636,46%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1483,72%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>191,54%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>62,91%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>555,33%</t>
+          <t>1496,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>833,11%</t>
+          <t>839,13%</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-66,27; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 1322,67</t>
+          <t>-34,85; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,89; 1500,0</t>
+          <t>-38,65; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 5880,91</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,19</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,41</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,55</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,92</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,07</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,41</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,38</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,85</t>
+          <t>3,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 3,49</t>
+          <t>-2,72; 2,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 1,89</t>
+          <t>-3,64; 0,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 9,97</t>
+          <t>-0,82; 16,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 2,04</t>
+          <t>-2,19; 3,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,84</t>
+          <t>-2,89; 1,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 13,81</t>
+          <t>-2,17; 10,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,28</t>
+          <t>-1,44; 2,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,07</t>
+          <t>-2,06; 1,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 8,72</t>
+          <t>-0,25; 10,55</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22,78%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-49,15%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>546,99%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>63,63%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>74,2%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>22,78%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-49,15%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>526,94%</t>
+          <t>101,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>253,6%</t>
+          <t>278,73%</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-75,57; 627,11</t>
+          <t>-76,46; 690,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-90,24; —</t>
+          <t>-89,93; 363,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,86</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4,49</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,55</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,04</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,86</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,2</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>3,31</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 0,0</t>
+          <t>-1,25; 1,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,04</t>
+          <t>0,65; 6,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 9,84</t>
+          <t>-0,42; 18,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,73</t>
+          <t>-2,75; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 6,44</t>
+          <t>-1,68; 1,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 20,67</t>
+          <t>-1,1; 8,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,66</t>
+          <t>-1,21; 0,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 3,32</t>
+          <t>-0,02; 3,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 11,7</t>
+          <t>0,19; 13,96</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>16,63%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>406,69%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>637,67%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-7,53%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>300,34%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>16,63%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>406,69%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>596,6%</t>
+          <t>241,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>522,62%</t>
+          <t>525,57%</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-43,3; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,21; 2613,76</t>
+          <t>-62,3; 2527,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,55</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,86</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3,96</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,23</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,54</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2,27</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,55</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,86</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,78</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,12</t>
+          <t>3,21</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,03</t>
+          <t>-0,18; 1,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,51</t>
+          <t>-0,04; 1,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 5,92</t>
+          <t>1,42; 10,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,4</t>
+          <t>-0,65; 1,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,8</t>
+          <t>-0,25; 1,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,2; 8,48</t>
+          <t>0,29; 6,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,96</t>
+          <t>-0,24; 0,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,4</t>
+          <t>0,08; 1,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,61</t>
+          <t>1,4; 6,15</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>97,26%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>151,78%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>701,86%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>36,36%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>86,94%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>365,61%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>97,26%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>151,78%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>669,03%</t>
+          <t>363,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>527,48%</t>
+          <t>542,17%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-70,37; 416,36</t>
+          <t>-32,26; 697,45</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,25; 664,98</t>
+          <t>-24,92; 732,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 1789,85</t>
+          <t>88,0; 3811,2</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-42,58; 602,17</t>
+          <t>-64,21; 378,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,23; 698,18</t>
+          <t>-45,36; 642,13</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,77; 2998,07</t>
+          <t>-25,93; 2111,86</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-26,17; 291,77</t>
+          <t>-31,19; 297,86</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,41; 499,06</t>
+          <t>-1,76; 386,27</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>145,15; 1477,68</t>
+          <t>145,17; 1492,17</t>
         </is>
       </c>
     </row>
